--- a/artfynd/A 21591-2025 artfynd.xlsx
+++ b/artfynd/A 21591-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101687921</v>
+        <v>1896389</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gles lövlund N om Brunnstorp, Sm</t>
+          <t>400 m NO Brunnstop (07E1c09), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462005.060168875</v>
+        <v>462115</v>
       </c>
       <c r="R2" t="n">
-        <v>6403438.31474271</v>
+        <v>6403316</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2001-12-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2001-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>070412091 / CYP INQU / Enstaka-sparsam (1)  / OBJ.AREA:2,9 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +765,261 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Uno Björkman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>101687921</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gles lövlund N om Brunnstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>462005</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6403438</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lekeryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>William Rosén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>William Rosén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117005771</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Äng/Hage N om Brunnstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>462016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6403291</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lekeryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>William Rosén, henrik kullberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21591-2025 artfynd.xlsx
+++ b/artfynd/A 21591-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1896389</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101687921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117005771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>